--- a/data/asset_classes_unconstrained.xlsx
+++ b/data/asset_classes_unconstrained.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evan_\OneDrive\1Evan\.eff_fron_spyder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26369F16-4966-4BC4-BF6A-434391D4B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F79A55-B33C-47ED-B201-06C3BCCC6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
-    <sheet name="Dates &amp;amp;amp;amp;amp;amp; Ris" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,16 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Risk Free Rate</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Ticker</t>
   </si>
@@ -91,8 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00%"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="#,##0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.000%"/>
   </numFmts>
@@ -138,26 +127,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -478,218 +449,144 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0</v>
-      </c>
-      <c r="C2" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8">
-        <v>0</v>
-      </c>
-      <c r="C8" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-      <c r="C9" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11">
-        <v>0.99999000000000005</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" style="6" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <f ca="1">DATE(YEAR(B2)-10,MONTH(B2),DAY(B2))</f>
-        <v>41864</v>
-      </c>
-      <c r="B2" s="3">
-        <f ca="1">NOW()</f>
-        <v>45517.664367129626</v>
-      </c>
-      <c r="C2" s="4">
-        <v>5.1499999999999997E-2</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.99999000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.99999000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/data/asset_classes_unconstrained.xlsx
+++ b/data/asset_classes_unconstrained.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evan_\OneDrive\1Evan\.eff_fron_spyder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F79A55-B33C-47ED-B201-06C3BCCC6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{89F79A55-B33C-47ED-B201-06C3BCCC6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414DC689-8380-41BB-A3B5-F3412DD82E53}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,8 +82,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="#,##0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000%"/>
+    <numFmt numFmtId="164" formatCode="#,##0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -129,19 +129,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -159,6 +159,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/asset_classes_unconstrained.xlsx
+++ b/data/asset_classes_unconstrained.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{89F79A55-B33C-47ED-B201-06C3BCCC6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414DC689-8380-41BB-A3B5-F3412DD82E53}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{89F79A55-B33C-47ED-B201-06C3BCCC6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756CB7D1-B4B0-448F-A176-ACBB8AF2D103}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Ticker</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>IAU</t>
+  </si>
+  <si>
+    <t>Curr Weight</t>
   </si>
 </sst>
 </file>
@@ -127,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -144,6 +147,9 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -159,10 +165,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,15 +455,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -483,7 +489,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -494,7 +500,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -505,7 +511,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -516,7 +522,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -527,7 +533,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -538,7 +544,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -549,7 +555,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -560,7 +566,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -571,7 +577,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -582,7 +588,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
